--- a/stories/arbres/TREE-COL-003.xlsx
+++ b/stories/arbres/TREE-COL-003.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jules est dans le jardin, avec papa. Maman apporte un tapis. Des copains veulent parler. Chacun son tour. Papa dit : on peut attendre. Puis on parle. On peut lever la main.</t>
+          <t>Jules est dans le jardin, avec papa. Maman apporte un tapis. Des copains veulent parler. Chacun son tour. On peut attendre. Puis on parle. On peut lever la main.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Jules est dans le jardin, avec papa. Maman apporte un tapis. Des copains veulent parler. Chacun son tour.
+papa|On peut attendre.
+narrateur|Puis on parle. On peut lever la main.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1515,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1515,7 +1544,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jules choisit le rouge. Un copain veut parler. Jules lève la main. Il attend. Puis il parle. Papa dit : c'est ton tour. On attend. Puis on parle.</t>
+          <t>Jules choisit le rouge. Un copain veut parler. Jules lève la main. Il attend. Puis il parle. C'est ton tour. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1682,13 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit le rouge. Un copain veut parler. Jules lève la main. Il attend. Puis il parle.
+papa|C'est ton tour. On attend.
+narrateur|Puis on parle.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1869,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On attend, puis on parle ?</t>
         </is>
       </c>
     </row>
@@ -2001,6 +2042,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On peut attendre. Puis on parle. Jules respire. Papa est là. On peut attendre. Puis on parle. On peut lever la main.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2187,6 +2233,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2211,7 +2262,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Jules a le ballon rouge. Un copain parle. Jules attend. Puis il parle. Il dit : à moi le ballon, s'il te plaît. On attend. Puis on parle. Papa montre le geste, lentement. On peut attendre. Puis on parle. On peut lever la main.</t>
+          <t>Jules a le ballon rouge. Un copain parle. Jules attend. Puis il parle. À moi le ballon, s'il te plaît. On attend. Puis on parle. Papa montre le geste, lentement. On peut attendre. Puis on parle. On peut lever la main.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2349,6 +2400,13 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a le ballon rouge. Un copain parle. Jules attend. Puis il parle.
+narrateur|À moi le ballon, s'il te plaît. On attend.
+narrateur|Puis on parle. Papa montre le geste, lentement. On peut attendre. Puis on parle. On peut lever la main.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2535,6 +2593,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2697,6 +2760,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi rouge. Puis le ballon rouge. Puis le chat. Le sol est un peu froid. Jules ferme le sac. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2927,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3094,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Jules s'arrête près de le chien. le ballon rouge est rangé. On range un objet. Jules tend le chien à maman. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3261,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3428,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Jules se souvient de rouge. Et de le ballon rouge. Et de la poule. On rit un peu. Jules ferme la porte, tout doux. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3595,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3531,7 +3624,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Jules a le seau bleu. Un copain parle. Jules lève la main. Il attend. Puis il parle. On attend. Puis on parle. Papa dit : je suis là. On peut attendre. Puis on parle. On peut lever la main.</t>
+          <t>Jules a le seau bleu. Un copain parle. Jules lève la main. Il attend. Puis il parle. On attend. Puis on parle. Je suis là. On peut attendre. Puis on parle. On peut lever la main.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3669,6 +3762,13 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a le seau bleu. Un copain parle. Jules lève la main. Il attend. Puis il parle. On attend. Puis on parle.
+papa|Je suis là. On peut attendre.
+narrateur|Puis on parle. On peut lever la main.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3855,6 +3955,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4017,6 +4122,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le chat. Après le seau bleu. Près de rouge. Jules s'arrête. L'eau coule, tout petit bruit. Jules boit une gorgée d'eau. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4289,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4456,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Jules range le seau bleu. le chien reste près de rouge. Un galet est encore chaud. Jules serre la main de papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4623,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4527,7 +4652,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>la poule est là. le seau bleu aussi. rouge reste dans le souvenir. Un ruban reste dans la poche. Jules raccroche un linge. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>La poule est là. le seau bleu aussi. rouge reste dans le souvenir. Un ruban reste dans la poche. Jules raccroche un linge. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4665,6 +4790,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|La poule est là. le seau bleu aussi. rouge reste dans le souvenir. Un ruban reste dans la poche. Jules raccroche un linge. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4957,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5124,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a le doudou. Un copain parle. Jules lève la main. Il attend. Puis il parle. On attend. Puis on parle. Papa reste tout près. On peut attendre. Puis on parle. On peut lever la main.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5175,6 +5315,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5337,6 +5482,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le chat. le doudou est rangé. rouge est fini. Ça sent le pain chaud. Jules souffle, puis sourit à papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5499,6 +5649,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5661,6 +5816,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Près de le chien. Jules pose le doudou. rouge est derrière. Une chaussette est encore sablée. Jules range encore un peu, près de papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5823,6 +5983,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5985,6 +6150,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Jules montre la poule. Papa a vu rouge. Et le doudou. La lumière est claire. Jules essuie ses mains. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6147,6 +6317,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6171,7 +6346,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Jules choisit le bleu. Une copine parle. Jules attend. Il lève la main. Puis il parle. Il dit : le bleu est pour le seau. Maman écoute jusqu'au bout.</t>
+          <t>Jules choisit le bleu. Une copine parle. Jules attend. Il lève la main. Puis il parle. Le bleu est pour le seau. Maman écoute jusqu'au bout.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6309,6 +6484,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit le bleu. Une copine parle. Jules attend. Il lève la main. Puis il parle.
+narrateur|Le bleu est pour le seau. Maman écoute jusqu'au bout.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6489,6 +6670,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|On lève la main, et on attend ?</t>
         </is>
       </c>
     </row>
@@ -6657,6 +6843,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On peut attendre. Puis on parle. Jules retient le geste. Papa sourit. On peut attendre. Puis on parle. On peut lever la main.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7034,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6867,7 +7063,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Jules a le ballon. Un chat passe. Un copain s'écrie. Jules attend. Puis il parle. On attend. Puis on parle. Papa dit : je suis là. On peut attendre. Puis on parle. On peut lever la main.</t>
+          <t>Jules a le ballon. Un chat passe. Un copain s'écrie. Jules attend. Puis il parle. On attend. Puis on parle. Je suis là. On peut attendre. Puis on parle. On peut lever la main.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7005,6 +7201,13 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a le ballon. Un chat passe. Un copain s'écrie. Jules attend. Puis il parle. On attend. Puis on parle.
+papa|Je suis là. On peut attendre.
+narrateur|Puis on parle. On peut lever la main.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7191,6 +7394,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7353,6 +7561,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi bleu. Puis le ballon rouge. Puis le chat. Il y a des miettes sur la table. Jules marche près de papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7515,6 +7728,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7677,6 +7895,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Jules s'arrête près de le chien. le ballon rouge est rangé. Un ballon s'immobilise. Jules plie un pull. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7839,6 +8062,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8001,6 +8229,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Jules se souvient de bleu. Et de le ballon rouge. Et de la poule. Le savon sent bon. Jules sourit. Papa sourit aussi. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8163,6 +8396,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8325,6 +8563,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a le seau. Un chat passe. Jules lève la main. Il attend. Puis il parle. On attend. Puis on parle. Papa reste tout près. On peut attendre. Puis on parle. On peut lever la main.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8511,6 +8754,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8673,6 +8921,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le chat. Après le seau bleu. Près de bleu. Jules s'arrête. Un linge sèche à l'air. Jules répète tout bas le geste. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8835,6 +9088,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8997,6 +9255,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Jules range le seau bleu. le chien reste près de bleu. Le vent est doux. Jules pose le seau bleu à sa place. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9159,6 +9422,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9183,7 +9451,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>la poule est là. le seau bleu aussi. bleu reste dans le souvenir. Une feuille tombe. Jules pose sa tête un moment. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>La poule est là. le seau bleu aussi. bleu reste dans le souvenir. Une feuille tombe. Jules pose sa tête un moment. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9321,6 +9589,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|La poule est là. le seau bleu aussi. bleu reste dans le souvenir. Une feuille tombe. Jules pose sa tête un moment. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9483,6 +9756,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9645,6 +9923,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a le doudou. Un chat passe. Jules lève la main. Il attend. Puis il parle. On attend. Puis on parle. Papa montre le geste, lentement. On peut attendre. Puis on parle. On peut lever la main.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9831,6 +10114,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9993,6 +10281,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le chat. le doudou est rangé. bleu est fini. On attend son tour. Jules s'assoit près de papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10155,6 +10448,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10317,6 +10615,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Près de le chien. Jules pose le doudou. bleu est derrière. Un vélo passe au loin. Jules montre le chien à papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10479,6 +10782,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10641,6 +10949,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Jules montre la poule. Papa a vu bleu. Et le doudou. On se tient la main. Jules enfile ses chaussons. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10803,6 +11116,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10827,7 +11145,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Jules choisit le vert. Les copains parlent fort. Jules lève la main. Il attend. Puis il parle. Papa dit : chacun son tour. On attend. Puis on parle.</t>
+          <t>Jules choisit le vert. Les copains parlent fort. Jules lève la main. Il attend. Puis il parle. Chacun son tour. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10965,6 +11283,13 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Jules choisit le vert. Les copains parlent fort. Jules lève la main. Il attend. Puis il parle.
+papa|Chacun son tour. On attend.
+narrateur|Puis on parle.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11141,6 +11466,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On parle tout de suite, ou on attend ?</t>
         </is>
       </c>
     </row>
@@ -11309,6 +11639,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On peut attendre. Puis on parle. Jules hoche la tête. On continue, avec papa. On peut attendre. Puis on parle. On peut lever la main.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11495,6 +11830,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11657,6 +11997,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a le ballon. Un chien aboie au loin. Jules attend. Puis il parle. On attend. Puis on parle. Papa reste tout près. On peut attendre. Puis on parle. On peut lever la main.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11843,6 +12188,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12005,6 +12355,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi vert. Puis le ballon rouge. Puis le chat. Un chat miaule une fois. Jules écoute papa encore une fois. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12167,6 +12522,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12191,7 +12551,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Jules s'arrête près de le chien. le ballon rouge est rangé. Une tasse cliquette. Jules dit : j'ai appris. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>Jules s'arrête près de le chien. le ballon rouge est rangé. Une tasse cliquette. J'ai appris. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12329,6 +12689,13 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Jules s'arrête près de le chien. le ballon rouge est rangé. Une tasse cliquette.
+enfant-m|J'ai appris. On peut attendre.
+narrateur|Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12491,6 +12858,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12653,6 +13025,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Jules se souvient de vert. Et de le ballon rouge. Et de la poule. Une pomme brille un peu. Jules range vert dans sa tête, comme un souvenir. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12815,6 +13192,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12977,6 +13359,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a le seau. Une poule caquette. Jules lève la main. Il attend. Puis il parle. On attend. Puis on parle. Papa montre le geste, lentement. On peut attendre. Puis on parle. On peut lever la main.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13163,6 +13550,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13325,6 +13717,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le chat. Après le seau bleu. Près de vert. Jules s'arrête. Les chaussures font toc toc. Jules chuchote : c'est fini. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13487,6 +13884,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13649,6 +14051,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Jules range le seau bleu. le chien reste près de vert. La couverture est douce. Jules dit merci à papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13811,6 +14218,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13835,7 +14247,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>la poule est là. le seau bleu aussi. vert reste dans le souvenir. On dit merci. Jules caresse le doudou. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>La poule est là. le seau bleu aussi. vert reste dans le souvenir. On dit merci. Jules caresse le doudou. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -13973,6 +14385,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|La poule est là. le seau bleu aussi. vert reste dans le souvenir. On dit merci. Jules caresse le doudou. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14135,6 +14552,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14159,7 +14581,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Jules a le doudou. Une poule caquette. Jules lève la main. Il attend. Puis il parle. On attend. Puis on parle. Papa dit : je suis là. On peut attendre. Puis on parle. On peut lever la main.</t>
+          <t>Jules a le doudou. Une poule caquette. Jules lève la main. Il attend. Puis il parle. On attend. Puis on parle. Je suis là. On peut attendre. Puis on parle. On peut lever la main.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14297,6 +14719,13 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a le doudou. Une poule caquette. Jules lève la main. Il attend. Puis il parle. On attend. Puis on parle.
+papa|Je suis là. On peut attendre.
+narrateur|Puis on parle. On peut lever la main.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14483,6 +14912,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14645,6 +15079,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le chat. le doudou est rangé. vert est fini. On écoute jusqu'au bout. Maman n'est pas loin. Jules les rejoint. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14807,6 +15246,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14969,6 +15413,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Près de le chien. Jules pose le doudou. vert est derrière. Un crochet tient bien le manteau. Jules range la tasse. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15131,6 +15580,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15293,6 +15747,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Jules montre la poule. Papa a vu vert. Et le doudou. On entend un oiseau. Jules prend la main de papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15455,6 +15914,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15473,7 +15937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15490,6 +15954,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>ch1: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-003.xlsx
+++ b/stories/arbres/TREE-COL-003.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Puis on parle. On peut lever la main.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1520,6 +1526,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1689,6 +1696,7 @@
 narrateur|Puis on parle.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1876,6 +1884,7 @@
           <t>narrateur|On attend, puis on parle ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2047,6 +2056,7 @@
           <t>narrateur|Oui. On peut attendre. Puis on parle. Jules respire. Papa est là. On peut attendre. Puis on parle. On peut lever la main.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2238,6 +2248,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2407,6 +2418,7 @@
 narrateur|Puis on parle. Papa montre le geste, lentement. On peut attendre. Puis on parle. On peut lever la main.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2596,6 +2608,11 @@
       <c r="AW9" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -2765,6 +2782,7 @@
           <t>narrateur|Jules a choisi rouge. Puis le ballon rouge. Puis le chat. Le sol est un peu froid. Jules ferme le sac. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2932,6 +2950,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3099,6 +3118,11 @@
           <t>narrateur|Jules s'arrête près de le chien. le ballon rouge est rangé. On range un objet. Jules tend le chien à maman. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3266,6 +3290,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3433,6 +3458,7 @@
           <t>narrateur|Jules se souvient de rouge. Et de le ballon rouge. Et de la poule. On rit un peu. Jules ferme la porte, tout doux. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3600,6 +3626,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3769,6 +3796,7 @@
 narrateur|Puis on parle. On peut lever la main.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3958,6 +3986,11 @@
       <c r="AW17" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -4127,6 +4160,7 @@
           <t>narrateur|Avec le chat. Après le seau bleu. Près de rouge. Jules s'arrête. L'eau coule, tout petit bruit. Jules boit une gorgée d'eau. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4294,6 +4328,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4461,6 +4496,11 @@
           <t>narrateur|Jules range le seau bleu. le chien reste près de rouge. Un galet est encore chaud. Jules serre la main de papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4628,6 +4668,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4795,6 +4836,7 @@
           <t>narrateur|La poule est là. le seau bleu aussi. rouge reste dans le souvenir. Un ruban reste dans la poche. Jules raccroche un linge. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4962,6 +5004,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5129,6 +5172,7 @@
           <t>narrateur|Jules a le doudou. Un copain parle. Jules lève la main. Il attend. Puis il parle. On attend. Puis on parle. Papa reste tout près. On peut attendre. Puis on parle. On peut lever la main.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5318,6 +5362,11 @@
       <c r="AW25" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -5487,6 +5536,7 @@
           <t>narrateur|Jules rejoint le chat. le doudou est rangé. rouge est fini. Ça sent le pain chaud. Jules souffle, puis sourit à papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5654,6 +5704,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5821,6 +5872,11 @@
           <t>narrateur|Près de le chien. Jules pose le doudou. rouge est derrière. Une chaussette est encore sablée. Jules range encore un peu, près de papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5988,6 +6044,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6155,6 +6212,7 @@
           <t>narrateur|Jules montre la poule. Papa a vu rouge. Et le doudou. La lumière est claire. Jules essuie ses mains. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6322,6 +6380,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6490,6 +6549,7 @@
 narrateur|Le bleu est pour le seau. Maman écoute jusqu'au bout.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6677,6 +6737,7 @@
           <t>narrateur|On lève la main, et on attend ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6848,6 +6909,7 @@
           <t>narrateur|Oui. On peut attendre. Puis on parle. Jules retient le geste. Papa sourit. On peut attendre. Puis on parle. On peut lever la main.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7039,6 +7101,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7208,6 +7271,7 @@
 narrateur|Puis on parle. On peut lever la main.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7397,6 +7461,11 @@
       <c r="AW37" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -7566,6 +7635,7 @@
           <t>narrateur|Jules a choisi bleu. Puis le ballon rouge. Puis le chat. Il y a des miettes sur la table. Jules marche près de papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7733,6 +7803,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7900,6 +7971,11 @@
           <t>narrateur|Jules s'arrête près de le chien. le ballon rouge est rangé. Un ballon s'immobilise. Jules plie un pull. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8067,6 +8143,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8234,6 +8311,7 @@
           <t>narrateur|Jules se souvient de bleu. Et de le ballon rouge. Et de la poule. Le savon sent bon. Jules sourit. Papa sourit aussi. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8401,6 +8479,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8568,6 +8647,7 @@
           <t>narrateur|Jules a le seau. Un chat passe. Jules lève la main. Il attend. Puis il parle. On attend. Puis on parle. Papa reste tout près. On peut attendre. Puis on parle. On peut lever la main.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8757,6 +8837,11 @@
       <c r="AW45" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -8926,6 +9011,7 @@
           <t>narrateur|Avec le chat. Après le seau bleu. Près de bleu. Jules s'arrête. Un linge sèche à l'air. Jules répète tout bas le geste. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9093,6 +9179,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9260,6 +9347,11 @@
           <t>narrateur|Jules range le seau bleu. le chien reste près de bleu. Le vent est doux. Jules pose le seau bleu à sa place. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9427,6 +9519,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9594,6 +9687,7 @@
           <t>narrateur|La poule est là. le seau bleu aussi. bleu reste dans le souvenir. Une feuille tombe. Jules pose sa tête un moment. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9761,6 +9855,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9928,6 +10023,7 @@
           <t>narrateur|Jules a le doudou. Un chat passe. Jules lève la main. Il attend. Puis il parle. On attend. Puis on parle. Papa montre le geste, lentement. On peut attendre. Puis on parle. On peut lever la main.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10117,6 +10213,11 @@
       <c r="AW53" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -10286,6 +10387,7 @@
           <t>narrateur|Jules rejoint le chat. le doudou est rangé. bleu est fini. On attend son tour. Jules s'assoit près de papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10453,6 +10555,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10620,6 +10723,11 @@
           <t>narrateur|Près de le chien. Jules pose le doudou. bleu est derrière. Un vélo passe au loin. Jules montre le chien à papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10787,6 +10895,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10954,6 +11063,7 @@
           <t>narrateur|Jules montre la poule. Papa a vu bleu. Et le doudou. On se tient la main. Jules enfile ses chaussons. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11121,6 +11231,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11290,6 +11401,7 @@
 narrateur|Puis on parle.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11473,6 +11585,7 @@
           <t>narrateur|On parle tout de suite, ou on attend ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11644,6 +11757,7 @@
           <t>narrateur|Oui. On peut attendre. Puis on parle. Jules hoche la tête. On continue, avec papa. On peut attendre. Puis on parle. On peut lever la main.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11835,6 +11949,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12002,6 +12117,11 @@
           <t>narrateur|Jules a le ballon. Un chien aboie au loin. Jules attend. Puis il parle. On attend. Puis on parle. Papa reste tout près. On peut attendre. Puis on parle. On peut lever la main.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12191,6 +12311,11 @@
       <c r="AW65" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -12360,6 +12485,7 @@
           <t>narrateur|Jules a choisi vert. Puis le ballon rouge. Puis le chat. Un chat miaule une fois. Jules écoute papa encore une fois. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12527,6 +12653,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12696,6 +12823,11 @@
 narrateur|Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12863,6 +12995,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13030,6 +13163,7 @@
           <t>narrateur|Jules se souvient de vert. Et de le ballon rouge. Et de la poule. Une pomme brille un peu. Jules range vert dans sa tête, comme un souvenir. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13197,6 +13331,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13364,6 +13499,7 @@
           <t>narrateur|Jules a le seau. Une poule caquette. Jules lève la main. Il attend. Puis il parle. On attend. Puis on parle. Papa montre le geste, lentement. On peut attendre. Puis on parle. On peut lever la main.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13553,6 +13689,11 @@
       <c r="AW73" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -13722,6 +13863,7 @@
           <t>narrateur|Avec le chat. Après le seau bleu. Près de vert. Jules s'arrête. Les chaussures font toc toc. Jules chuchote : c'est fini. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13889,6 +14031,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14056,6 +14199,11 @@
           <t>narrateur|Jules range le seau bleu. le chien reste près de vert. La couverture est douce. Jules dit merci à papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14223,6 +14371,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14390,6 +14539,7 @@
           <t>narrateur|La poule est là. le seau bleu aussi. vert reste dans le souvenir. On dit merci. Jules caresse le doudou. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14557,6 +14707,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14726,6 +14877,7 @@
 narrateur|Puis on parle. On peut lever la main.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14915,6 +15067,11 @@
       <c r="AW81" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -15084,6 +15241,7 @@
           <t>narrateur|Jules rejoint le chat. le doudou est rangé. vert est fini. On écoute jusqu'au bout. Maman n'est pas loin. Jules les rejoint. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15251,6 +15409,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15418,6 +15577,11 @@
           <t>narrateur|Près de le chien. Jules pose le doudou. vert est derrière. Un crochet tient bien le manteau. Jules range la tasse. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15585,6 +15749,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15752,6 +15917,7 @@
           <t>narrateur|Jules montre la poule. Papa a vu vert. Et le doudou. On entend un oiseau. Jules prend la main de papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15919,6 +16085,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15937,7 +16104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15961,6 +16128,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15975,7 +16156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16162,6 +16343,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-COL-003.xlsx
+++ b/stories/arbres/TREE-COL-003.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tour de parole — dans le jardin</t>
+          <t>L'arrosoir et le tapis</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sous le cerisier, Nino s'assoit sur le tapis. Il a une chose à dire. Il lève la main, il attend, puis il parle, avec papa et maman.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jules est dans le jardin, avec papa. Maman apporte un tapis. Des copains veulent parler. Chacun son tour. On peut attendre. Puis on parle. On peut lever la main.</t>
+          <t>L'arrosoir penche encore, près du cerisier. Une goutte tombe. Elle fait ploc dans l'herbe. L'herbe sent le vert, tout chaud. Un oiseau picore une cerise trop mûre. Le jus tache la terre, tout rouge. Une nappe à carreaux attend sous l'arbre. Papa pose une carafe. L'eau brille, un peu froide. Maman secoue le tapis. Le tapis est rêche, puis doux. Trois coussins sont là. Un rouge, un bleu, un vert. Nino, viens. Le jardin est à nous, ce matin. Le tapis est prêt. On s'assoit. En ce moment, Nino pose un genou sur le tapis. Le tapis chatouille un peu. J'ai une chose à dire. Moi aussi, j'ai une chose. On attend. Puis on parle. Tu peux lever la main. Papa parle déjà, tout doucement. Nino lève la main. Il attend. Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,12 +1337,41 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Jules est dans le jardin, avec papa. Maman apporte un tapis. Des copains veulent parler. Chacun son tour.
-papa|On peut attendre.
-narrateur|Puis on parle. On peut lever la main.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|L'arrosoir penche encore, près du cerisier.
+narrateur|Une goutte tombe.
+narrateur|Elle fait ploc dans l'herbe.
+narrateur|L'herbe sent le vert, tout chaud.
+narrateur|Un oiseau picore une cerise trop mûre.
+narrateur|Le jus tache la terre, tout rouge.
+narrateur|Une nappe à carreaux attend sous l'arbre.
+narrateur|Papa pose une carafe.
+narrateur|L'eau brille, un peu froide.
+narrateur|Maman secoue le tapis.
+narrateur|Le tapis est rêche, puis doux.
+narrateur|Trois coussins sont là.
+narrateur|Un rouge, un bleu, un vert.
+papa|Nino, viens.
+papa|Le jardin est à nous, ce matin.
+maman|Le tapis est prêt.
+maman|On s'assoit.
+narrateur|En ce moment, Nino pose un genou sur le tapis.
+narrateur|Le tapis chatouille un peu.
+enfant-m|J'ai une chose à dire.
+papa|Moi aussi, j'ai une chose.
+papa|On attend.
+papa|Puis on parle.
+maman|Tu peux lever la main.
+narrateur|Papa parle déjà, tout doucement.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+narrateur|Le cerisier fait une ombre ronde.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>goutte,oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1355,7 +1396,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre rouge, bleu, ou vert.</t>
+          <t>Le tapis a trois coussins tout proches. Rouge, bleu, ou vert ? On s'assoit. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1523,7 +1564,11 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+          <t>narrateur|Le tapis a trois coussins tout proches.
+papa|Rouge, bleu, ou vert ?
+maman|On s'assoit.
+maman|On attend.
+maman|Puis on parle.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1551,7 +1596,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jules choisit le rouge. Un copain veut parler. Jules lève la main. Il attend. Puis il parle. C'est ton tour. On attend. Puis on parle.</t>
+          <t>Nino choisit le coussin rouge. Le tissu est chaud, comme le soleil. Un fil rouge dépasse, tout doux. Moi, je raconte le cerisier. Papa parle. Nino a une chose à dire. Il lève la main. Il attend. C'est mon tour ? Oui. C'est ton tour. On a attendu. Puis on parle. Nino parle, tout doucement. Le coussin est chaud. Bravo, Nino. Tu as attendu. Puis tu as parlé.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1691,9 +1736,23 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Jules choisit le rouge. Un copain veut parler. Jules lève la main. Il attend. Puis il parle.
-papa|C'est ton tour. On attend.
-narrateur|Puis on parle.</t>
+          <t>narrateur|Nino choisit le coussin rouge.
+narrateur|Le tissu est chaud, comme le soleil.
+narrateur|Un fil rouge dépasse, tout doux.
+papa|Moi, je raconte le cerisier.
+narrateur|Papa parle.
+narrateur|Nino a une chose à dire.
+narrateur|Il lève la main.
+narrateur|Il attend.
+enfant-m|C'est mon tour ?
+papa|Oui. C'est ton tour.
+papa|On a attendu.
+papa|Puis on parle.
+narrateur|Nino parle, tout doucement.
+enfant-m|Le coussin est chaud.
+maman|Bravo, Nino.
+maman|Tu as attendu.
+maman|Puis tu as parlé.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1721,7 +1780,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>On attend, puis on parle ?</t>
+          <t>Nino veut parler. Il fait quoi d'abord ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1881,7 +1940,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|On attend, puis on parle ?</t>
+          <t>narrateur|Nino veut parler.
+papa|Il fait quoi d'abord ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1909,7 +1969,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. On peut attendre. Puis on parle. Jules respire. Papa est là. On peut attendre. Puis on parle. On peut lever la main.</t>
+          <t>Oui. On attend. Puis on parle. Nino souffle un peu. Sa main redescend, tout doux. J'ai attendu. Bravo. Tu peux lever la main, la prochaine fois aussi. C'est du bon travail, Nino.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2053,7 +2113,15 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On peut attendre. Puis on parle. Jules respire. Papa est là. On peut attendre. Puis on parle. On peut lever la main.</t>
+          <t>papa|Oui.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Nino souffle un peu.
+narrateur|Sa main redescend, tout doux.
+enfant-m|J'ai attendu.
+maman|Bravo.
+maman|Tu peux lever la main, la prochaine fois aussi.
+papa|C'est du bon travail, Nino.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2081,7 +2149,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>Près du tapis, trois jouets attendent. Le ballon rouge, le seau bleu, ou le doudou ? On joue. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2245,7 +2313,11 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>narrateur|Près du tapis, trois jouets attendent.
+maman|Le ballon rouge, le seau bleu, ou le doudou ?
+papa|On joue.
+papa|On attend.
+papa|Puis on parle.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2273,7 +2345,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Jules a le ballon rouge. Un copain parle. Jules attend. Puis il parle. À moi le ballon, s'il te plaît. On attend. Puis on parle. Papa montre le geste, lentement. On peut attendre. Puis on parle. On peut lever la main.</t>
+          <t>Nino prend le ballon rouge. Le ballon est un peu sablé. Il fait poum contre le tapis. J'ai une règle pour le ballon. Papa parle. Nino lève la main. Il attend. C'est ton tour. Le ballon, s'il te plaît. Oui. Merci d'avoir attendu. On attend. Puis on parle. Nino tient le ballon contre son ventre. Bravo. Un rayon rouge reste sur le ballon. Le coussin rouge reste sous le genou. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2413,12 +2485,31 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Jules a le ballon rouge. Un copain parle. Jules attend. Puis il parle.
-narrateur|À moi le ballon, s'il te plaît. On attend.
-narrateur|Puis on parle. Papa montre le geste, lentement. On peut attendre. Puis on parle. On peut lever la main.</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+          <t>narrateur|Nino prend le ballon rouge.
+narrateur|Le ballon est un peu sablé.
+narrateur|Il fait poum contre le tapis.
+papa|J'ai une règle pour le ballon.
+narrateur|Papa parle.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+papa|C'est ton tour.
+enfant-m|Le ballon, s'il te plaît.
+maman|Oui. Merci d'avoir attendu.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Nino tient le ballon contre son ventre.
+maman|Bravo.
+narrateur|Un rayon rouge reste sur le ballon.
+narrateur|Le coussin rouge reste sous le genou.
+papa|On attend.
+papa|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2443,7 +2534,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>Au fond du jardin, trois animaux sont là. Le chat, le chien, ou la poule ? On dit bonjour. Chacun son tour.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2607,7 +2698,10 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|Au fond du jardin, trois animaux sont là.
+papa|Le chat, le chien, ou la poule ?
+maman|On dit bonjour.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -2639,7 +2733,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi rouge. Puis le ballon rouge. Puis le chat. Le sol est un peu froid. Jules ferme le sac. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>Le chat s'étire sur la pierre chaude. Ses moustaches bougent. Il fait un petit rrr, tout bas. Nino a encore le ballon rouge près du coussin rouge. Un rayon rouge reste sur le ballon, près du chat. On dit bonjour à le chat. Nino lève la main. Il attend. Bonjour. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans le jardin aussi. Merci, papa. Merci, maman. Nino pose le ballon rouge sur le tapis. Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2779,7 +2873,23 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi rouge. Puis le ballon rouge. Puis le chat. Le sol est un peu froid. Jules ferme le sac. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>narrateur|Le chat s'étire sur la pierre chaude.
+narrateur|Ses moustaches bougent.
+narrateur|Il fait un petit rrr, tout bas.
+narrateur|Nino a encore le ballon rouge près du coussin rouge.
+narrateur|Un rayon rouge reste sur le ballon, près du chat.
+papa|On dit bonjour à le chat.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans le jardin aussi.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Nino pose le ballon rouge sur le tapis.
+narrateur|Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2807,7 +2917,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Nino a choisi le rouge, le ballon rouge, et le chat. Bravo, Nino. C'est du bon travail. Le chat s'endort sur la pierre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2947,7 +3057,13 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Nino a choisi le rouge, le ballon rouge, et le chat.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le chat s'endort sur la pierre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2975,7 +3091,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Jules s'arrête près de le chien. le ballon rouge est rangé. On range un objet. Jules tend le chien à maman. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>Le chien remue la queue. Son collier fait un toc léger. Il fait wouaf, tout doux. Nino a encore le ballon rouge près du coussin rouge. Le chien pose le nez sur le ballon. On dit bonjour à le chien. Nino lève la main. Il attend. Bonjour. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans le jardin aussi. Merci, papa. Merci, maman. Nino pose le ballon rouge sur le tapis. Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3115,7 +3231,23 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Jules s'arrête près de le chien. le ballon rouge est rangé. On range un objet. Jules tend le chien à maman. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>narrateur|Le chien remue la queue.
+narrateur|Son collier fait un toc léger.
+narrateur|Il fait wouaf, tout doux.
+narrateur|Nino a encore le ballon rouge près du coussin rouge.
+narrateur|Le chien pose le nez sur le ballon.
+papa|On dit bonjour à le chien.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans le jardin aussi.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Nino pose le ballon rouge sur le tapis.
+narrateur|Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -3147,7 +3279,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Nino a choisi le rouge, le ballon rouge, et le chien. Bravo, Nino. C'est du bon travail. Le chien remue encore la queue, tout lentement. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3287,7 +3419,13 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Nino a choisi le rouge, le ballon rouge, et le chien.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le chien remue encore la queue, tout lentement.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3315,7 +3453,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Jules se souvient de rouge. Et de le ballon rouge. Et de la poule. On rit un peu. Jules ferme la porte, tout doux. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>La poule picore près de la haie. Elle fait cot cot, tout petit. Une plume blonde reste dans l'herbe. Nino a encore le ballon rouge près du coussin rouge. Une petite plume colle au ballon. On dit bonjour à la poule. Nino lève la main. Il attend. Bonjour. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans le jardin aussi. Merci, papa. Merci, maman. Nino pose le ballon rouge sur le tapis. Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3455,7 +3593,23 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Jules se souvient de rouge. Et de le ballon rouge. Et de la poule. On rit un peu. Jules ferme la porte, tout doux. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>narrateur|La poule picore près de la haie.
+narrateur|Elle fait cot cot, tout petit.
+narrateur|Une plume blonde reste dans l'herbe.
+narrateur|Nino a encore le ballon rouge près du coussin rouge.
+narrateur|Une petite plume colle au ballon.
+papa|On dit bonjour à la poule.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans le jardin aussi.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Nino pose le ballon rouge sur le tapis.
+narrateur|Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3483,7 +3637,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Nino a choisi le rouge, le ballon rouge, et la poule. Bravo, Nino. C'est du bon travail. La poule picore encore un grain, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3623,7 +3777,13 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Nino a choisi le rouge, le ballon rouge, et la poule.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La poule picore encore un grain, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3651,7 +3811,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Jules a le seau bleu. Un copain parle. Jules lève la main. Il attend. Puis il parle. On attend. Puis on parle. Je suis là. On peut attendre. Puis on parle. On peut lever la main.</t>
+          <t>Nino prend le seau bleu. Un peu d'eau tremble au fond. Le seau sonne, tout creux. Moi, je raconte l'eau de l'arrosoir. Maman parle. Nino lève la main. Il attend. Je peux verser ? Oui. C'est ton tour. On a attendu. Puis on parle. Nino pose le seau près du tapis. Bravo, Nino. Tu as levé la main. Le seau a un reflet rouge, tout petit. Le coussin rouge reste sous le genou. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3791,12 +3951,31 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Jules a le seau bleu. Un copain parle. Jules lève la main. Il attend. Puis il parle. On attend. Puis on parle.
-papa|Je suis là. On peut attendre.
-narrateur|Puis on parle. On peut lever la main.</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr"/>
+          <t>narrateur|Nino prend le seau bleu.
+narrateur|Un peu d'eau tremble au fond.
+narrateur|Le seau sonne, tout creux.
+maman|Moi, je raconte l'eau de l'arrosoir.
+narrateur|Maman parle.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Je peux verser ?
+papa|Oui. C'est ton tour.
+papa|On a attendu.
+papa|Puis on parle.
+narrateur|Nino pose le seau près du tapis.
+maman|Bravo, Nino.
+maman|Tu as levé la main.
+narrateur|Le seau a un reflet rouge, tout petit.
+narrateur|Le coussin rouge reste sous le genou.
+papa|On attend.
+papa|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>seau</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3821,7 +4000,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>Au fond du jardin, trois animaux sont là. Le chat, le chien, ou la poule ? On dit bonjour. Chacun son tour.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3985,7 +4164,10 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|Au fond du jardin, trois animaux sont là.
+papa|Le chat, le chien, ou la poule ?
+maman|On dit bonjour.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -4017,7 +4199,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Avec le chat. Après le seau bleu. Près de rouge. Jules s'arrête. L'eau coule, tout petit bruit. Jules boit une gorgée d'eau. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>Le chat s'étire sur la pierre chaude. Ses moustaches bougent. Il fait un petit rrr, tout bas. Nino a encore le seau bleu près du coussin rouge. Le chat regarde l'eau du seau. On dit bonjour à le chat. Nino lève la main. Il attend. Bonjour. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans le jardin aussi. Merci, papa. Merci, maman. Nino pose le seau bleu sur le tapis. Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4157,7 +4339,23 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Avec le chat. Après le seau bleu. Près de rouge. Jules s'arrête. L'eau coule, tout petit bruit. Jules boit une gorgée d'eau. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>narrateur|Le chat s'étire sur la pierre chaude.
+narrateur|Ses moustaches bougent.
+narrateur|Il fait un petit rrr, tout bas.
+narrateur|Nino a encore le seau bleu près du coussin rouge.
+narrateur|Le chat regarde l'eau du seau.
+papa|On dit bonjour à le chat.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans le jardin aussi.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Nino pose le seau bleu sur le tapis.
+narrateur|Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4185,7 +4383,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Nino a choisi le rouge, le seau bleu, et le chat. Bravo, Nino. C'est du bon travail. Le chat s'endort sur la pierre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4325,7 +4523,13 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Nino a choisi le rouge, le seau bleu, et le chat.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le chat s'endort sur la pierre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4353,7 +4557,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Jules range le seau bleu. le chien reste près de rouge. Un galet est encore chaud. Jules serre la main de papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>Le chien remue la queue. Son collier fait un toc léger. Il fait wouaf, tout doux. Nino a encore le seau bleu près du coussin rouge. Le chien lape une goutte, tout doux. On dit bonjour à le chien. Nino lève la main. Il attend. Bonjour. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans le jardin aussi. Merci, papa. Merci, maman. Nino pose le seau bleu sur le tapis. Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4493,7 +4697,23 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Jules range le seau bleu. le chien reste près de rouge. Un galet est encore chaud. Jules serre la main de papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>narrateur|Le chien remue la queue.
+narrateur|Son collier fait un toc léger.
+narrateur|Il fait wouaf, tout doux.
+narrateur|Nino a encore le seau bleu près du coussin rouge.
+narrateur|Le chien lape une goutte, tout doux.
+papa|On dit bonjour à le chien.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans le jardin aussi.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Nino pose le seau bleu sur le tapis.
+narrateur|Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -4525,7 +4745,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Nino a choisi le rouge, le seau bleu, et le chien. Bravo, Nino. C'est du bon travail. Le chien remue encore la queue, tout lentement. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4665,7 +4885,13 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Nino a choisi le rouge, le seau bleu, et le chien.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le chien remue encore la queue, tout lentement.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4693,7 +4919,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>La poule est là. le seau bleu aussi. rouge reste dans le souvenir. Un ruban reste dans la poche. Jules raccroche un linge. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>La poule picore près de la haie. Elle fait cot cot, tout petit. Une plume blonde reste dans l'herbe. Nino a encore le seau bleu près du coussin rouge. Un grain de mil est dans le seau. On dit bonjour à la poule. Nino lève la main. Il attend. Bonjour. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans le jardin aussi. Merci, papa. Merci, maman. Nino pose le seau bleu sur le tapis. Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4833,7 +5059,23 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|La poule est là. le seau bleu aussi. rouge reste dans le souvenir. Un ruban reste dans la poche. Jules raccroche un linge. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>narrateur|La poule picore près de la haie.
+narrateur|Elle fait cot cot, tout petit.
+narrateur|Une plume blonde reste dans l'herbe.
+narrateur|Nino a encore le seau bleu près du coussin rouge.
+narrateur|Un grain de mil est dans le seau.
+papa|On dit bonjour à la poule.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans le jardin aussi.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Nino pose le seau bleu sur le tapis.
+narrateur|Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4861,7 +5103,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Nino a choisi le rouge, le seau bleu, et la poule. Bravo, Nino. C'est du bon travail. La poule picore encore un grain, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5001,7 +5243,13 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Nino a choisi le rouge, le seau bleu, et la poule.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La poule picore encore un grain, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5029,7 +5277,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Jules a le doudou. Un copain parle. Jules lève la main. Il attend. Puis il parle. On attend. Puis on parle. Papa reste tout près. On peut attendre. Puis on parle. On peut lever la main.</t>
+          <t>Nino prend le doudou. Le doudou est gris, un peu sablé. Une oreille est encore chaude. Le doudou attend, lui aussi. Papa parle tout près. Nino lève la main. Il attend. Le doudou veut parler. Toi d'abord. On attend. Puis on parle. Bravo. Tu as attendu ton tour. Nino serre le doudou, tout doux. Le doudou touche le coussin rouge. Le coussin rouge reste sous le genou. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5169,7 +5417,24 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Jules a le doudou. Un copain parle. Jules lève la main. Il attend. Puis il parle. On attend. Puis on parle. Papa reste tout près. On peut attendre. Puis on parle. On peut lever la main.</t>
+          <t>narrateur|Nino prend le doudou.
+narrateur|Le doudou est gris, un peu sablé.
+narrateur|Une oreille est encore chaude.
+papa|Le doudou attend, lui aussi.
+narrateur|Papa parle tout près.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Le doudou veut parler.
+maman|Toi d'abord.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo.
+papa|Tu as attendu ton tour.
+narrateur|Nino serre le doudou, tout doux.
+narrateur|Le doudou touche le coussin rouge.
+narrateur|Le coussin rouge reste sous le genou.
+papa|On attend.
+papa|Puis on parle.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5197,7 +5462,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>Au fond du jardin, trois animaux sont là. Le chat, le chien, ou la poule ? On dit bonjour. Chacun son tour.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5361,7 +5626,10 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|Au fond du jardin, trois animaux sont là.
+papa|Le chat, le chien, ou la poule ?
+maman|On dit bonjour.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -5393,7 +5661,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le chat. le doudou est rangé. rouge est fini. Ça sent le pain chaud. Jules souffle, puis sourit à papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>Le chat s'étire sur la pierre chaude. Ses moustaches bougent. Il fait un petit rrr, tout bas. Nino a encore le doudou près du coussin rouge. Le chat se frotte au doudou. On dit bonjour à le chat. Nino lève la main. Il attend. Bonjour. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans le jardin aussi. Merci, papa. Merci, maman. Nino pose le doudou sur le tapis. Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5533,7 +5801,23 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le chat. le doudou est rangé. rouge est fini. Ça sent le pain chaud. Jules souffle, puis sourit à papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>narrateur|Le chat s'étire sur la pierre chaude.
+narrateur|Ses moustaches bougent.
+narrateur|Il fait un petit rrr, tout bas.
+narrateur|Nino a encore le doudou près du coussin rouge.
+narrateur|Le chat se frotte au doudou.
+papa|On dit bonjour à le chat.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans le jardin aussi.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Nino pose le doudou sur le tapis.
+narrateur|Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5561,7 +5845,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Nino a choisi le rouge, le doudou, et le chat. Bravo, Nino. C'est du bon travail. Le chat s'endort sur la pierre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5701,7 +5985,13 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Nino a choisi le rouge, le doudou, et le chat.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le chat s'endort sur la pierre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5729,7 +6019,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Près de le chien. Jules pose le doudou. rouge est derrière. Une chaussette est encore sablée. Jules range encore un peu, près de papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>Le chien remue la queue. Son collier fait un toc léger. Il fait wouaf, tout doux. Nino a encore le doudou près du coussin rouge. Le doudou sent le chien, un peu. On dit bonjour à le chien. Nino lève la main. Il attend. Bonjour. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans le jardin aussi. Merci, papa. Merci, maman. Nino pose le doudou sur le tapis. Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5869,7 +6159,23 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Près de le chien. Jules pose le doudou. rouge est derrière. Une chaussette est encore sablée. Jules range encore un peu, près de papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>narrateur|Le chien remue la queue.
+narrateur|Son collier fait un toc léger.
+narrateur|Il fait wouaf, tout doux.
+narrateur|Nino a encore le doudou près du coussin rouge.
+narrateur|Le doudou sent le chien, un peu.
+papa|On dit bonjour à le chien.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans le jardin aussi.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Nino pose le doudou sur le tapis.
+narrateur|Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -5901,7 +6207,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Nino a choisi le rouge, le doudou, et le chien. Bravo, Nino. C'est du bon travail. Le chien remue encore la queue, tout lentement. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6041,7 +6347,13 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Nino a choisi le rouge, le doudou, et le chien.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le chien remue encore la queue, tout lentement.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6069,7 +6381,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Jules montre la poule. Papa a vu rouge. Et le doudou. La lumière est claire. Jules essuie ses mains. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>La poule picore près de la haie. Elle fait cot cot, tout petit. Une plume blonde reste dans l'herbe. Nino a encore le doudou près du coussin rouge. La poule picore loin du doudou. On dit bonjour à la poule. Nino lève la main. Il attend. Bonjour. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans le jardin aussi. Merci, papa. Merci, maman. Nino pose le doudou sur le tapis. Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6209,7 +6521,23 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Jules montre la poule. Papa a vu rouge. Et le doudou. La lumière est claire. Jules essuie ses mains. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>narrateur|La poule picore près de la haie.
+narrateur|Elle fait cot cot, tout petit.
+narrateur|Une plume blonde reste dans l'herbe.
+narrateur|Nino a encore le doudou près du coussin rouge.
+narrateur|La poule picore loin du doudou.
+papa|On dit bonjour à la poule.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans le jardin aussi.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Nino pose le doudou sur le tapis.
+narrateur|Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6237,7 +6565,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Nino a choisi le rouge, le doudou, et la poule. Bravo, Nino. C'est du bon travail. La poule picore encore un grain, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6377,7 +6705,13 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Nino a choisi le rouge, le doudou, et la poule.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La poule picore encore un grain, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6405,7 +6739,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Jules choisit le bleu. Une copine parle. Jules attend. Il lève la main. Puis il parle. Le bleu est pour le seau. Maman écoute jusqu'au bout.</t>
+          <t>Nino choisit le coussin bleu. Le tissu est frais, comme la carafe. Un fil bleu chatouille le poignet. Moi, je raconte l'oiseau. Maman parle jusqu'au bout. Nino lève la main. Il attend. Le bleu, c'est l'eau. Oui. Merci d'avoir attendu. On lève la main. On attend. Puis on parle. Nino pose la paume sur le coussin. Le bleu est un peu froid. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6545,8 +6879,22 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Jules choisit le bleu. Une copine parle. Jules attend. Il lève la main. Puis il parle.
-narrateur|Le bleu est pour le seau. Maman écoute jusqu'au bout.</t>
+          <t>narrateur|Nino choisit le coussin bleu.
+narrateur|Le tissu est frais, comme la carafe.
+narrateur|Un fil bleu chatouille le poignet.
+maman|Moi, je raconte l'oiseau.
+narrateur|Maman parle jusqu'au bout.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Le bleu, c'est l'eau.
+maman|Oui. Merci d'avoir attendu.
+papa|On lève la main.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Nino pose la paume sur le coussin.
+narrateur|Le bleu est un peu froid.
+maman|Bravo.
+maman|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr"/>
@@ -6574,7 +6922,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>On lève la main, et on attend ?</t>
+          <t>Nino lève la main. Et après, on attend ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6734,7 +7082,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|On lève la main, et on attend ?</t>
+          <t>narrateur|Nino lève la main.
+maman|Et après, on attend ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6762,7 +7111,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. On peut attendre. Puis on parle. Jules retient le geste. Papa sourit. On peut attendre. Puis on parle. On peut lever la main.</t>
+          <t>Oui. On lève la main. On attend. Puis on parle. Nino retient encore le geste, tout petit. J'attends. Bravo. Le coussin bleu est à toi, et le tour aussi.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6906,7 +7255,14 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On peut attendre. Puis on parle. Jules retient le geste. Papa sourit. On peut attendre. Puis on parle. On peut lever la main.</t>
+          <t>maman|Oui.
+maman|On lève la main.
+maman|On attend.
+maman|Puis on parle.
+narrateur|Nino retient encore le geste, tout petit.
+enfant-m|J'attends.
+papa|Bravo.
+papa|Le coussin bleu est à toi, et le tour aussi.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6934,7 +7290,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>Près du tapis, trois jouets attendent. Le ballon rouge, le seau bleu, ou le doudou ? On joue. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7098,7 +7454,11 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>narrateur|Près du tapis, trois jouets attendent.
+maman|Le ballon rouge, le seau bleu, ou le doudou ?
+papa|On joue.
+papa|On attend.
+papa|Puis on parle.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7126,7 +7486,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Jules a le ballon. Un chat passe. Un copain s'écrie. Jules attend. Puis il parle. On attend. Puis on parle. Je suis là. On peut attendre. Puis on parle. On peut lever la main.</t>
+          <t>Nino prend le ballon rouge. Le ballon est un peu sablé. Il fait poum contre le tapis. J'ai une règle pour le ballon. Papa parle. Nino lève la main. Il attend. C'est ton tour. Le ballon, s'il te plaît. Oui. Merci d'avoir attendu. On attend. Puis on parle. Nino tient le ballon contre son ventre. Bravo. Le ballon roule vers le coussin bleu. Le coussin bleu reste sous le genou. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7266,12 +7626,31 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Jules a le ballon. Un chat passe. Un copain s'écrie. Jules attend. Puis il parle. On attend. Puis on parle.
-papa|Je suis là. On peut attendre.
-narrateur|Puis on parle. On peut lever la main.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|Nino prend le ballon rouge.
+narrateur|Le ballon est un peu sablé.
+narrateur|Il fait poum contre le tapis.
+papa|J'ai une règle pour le ballon.
+narrateur|Papa parle.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+papa|C'est ton tour.
+enfant-m|Le ballon, s'il te plaît.
+maman|Oui. Merci d'avoir attendu.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Nino tient le ballon contre son ventre.
+maman|Bravo.
+narrateur|Le ballon roule vers le coussin bleu.
+narrateur|Le coussin bleu reste sous le genou.
+papa|On attend.
+papa|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7296,7 +7675,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>Au fond du jardin, trois animaux sont là. Le chat, le chien, ou la poule ? On dit bonjour. Chacun son tour.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7460,7 +7839,10 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|Au fond du jardin, trois animaux sont là.
+papa|Le chat, le chien, ou la poule ?
+maman|On dit bonjour.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
@@ -7492,7 +7874,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi bleu. Puis le ballon rouge. Puis le chat. Il y a des miettes sur la table. Jules marche près de papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>Le chat s'étire sur la pierre chaude. Ses moustaches bougent. Il fait un petit rrr, tout bas. Nino a encore le ballon rouge près du coussin bleu. Le ballon roule vers la pierre bleue. On dit bonjour à le chat. Nino lève la main. Il attend. Bonjour. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans le jardin aussi. Merci, papa. Merci, maman. Nino pose le ballon rouge sur le tapis. Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7632,7 +8014,23 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi bleu. Puis le ballon rouge. Puis le chat. Il y a des miettes sur la table. Jules marche près de papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>narrateur|Le chat s'étire sur la pierre chaude.
+narrateur|Ses moustaches bougent.
+narrateur|Il fait un petit rrr, tout bas.
+narrateur|Nino a encore le ballon rouge près du coussin bleu.
+narrateur|Le ballon roule vers la pierre bleue.
+papa|On dit bonjour à le chat.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans le jardin aussi.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Nino pose le ballon rouge sur le tapis.
+narrateur|Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7660,7 +8058,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Nino a choisi le bleu, le ballon rouge, et le chat. Bravo, Nino. C'est du bon travail. Le chat s'endort sur la pierre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7800,7 +8198,13 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Nino a choisi le bleu, le ballon rouge, et le chat.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le chat s'endort sur la pierre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7828,7 +8232,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Jules s'arrête près de le chien. le ballon rouge est rangé. Un ballon s'immobilise. Jules plie un pull. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>Le chien remue la queue. Son collier fait un toc léger. Il fait wouaf, tout doux. Nino a encore le ballon rouge près du coussin bleu. Le collier du chien brille, un peu bleu. On dit bonjour à le chien. Nino lève la main. Il attend. Bonjour. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans le jardin aussi. Merci, papa. Merci, maman. Nino pose le ballon rouge sur le tapis. Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7968,7 +8372,23 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Jules s'arrête près de le chien. le ballon rouge est rangé. Un ballon s'immobilise. Jules plie un pull. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>narrateur|Le chien remue la queue.
+narrateur|Son collier fait un toc léger.
+narrateur|Il fait wouaf, tout doux.
+narrateur|Nino a encore le ballon rouge près du coussin bleu.
+narrateur|Le collier du chien brille, un peu bleu.
+papa|On dit bonjour à le chien.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans le jardin aussi.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Nino pose le ballon rouge sur le tapis.
+narrateur|Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -8000,7 +8420,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Nino a choisi le bleu, le ballon rouge, et le chien. Bravo, Nino. C'est du bon travail. Le chien remue encore la queue, tout lentement. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8140,7 +8560,13 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Nino a choisi le bleu, le ballon rouge, et le chien.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le chien remue encore la queue, tout lentement.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8168,7 +8594,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Jules se souvient de bleu. Et de le ballon rouge. Et de la poule. Le savon sent bon. Jules sourit. Papa sourit aussi. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>La poule picore près de la haie. Elle fait cot cot, tout petit. Une plume blonde reste dans l'herbe. Nino a encore le ballon rouge près du coussin bleu. L'eau de la carafe tremble près du ballon. On dit bonjour à la poule. Nino lève la main. Il attend. Bonjour. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans le jardin aussi. Merci, papa. Merci, maman. Nino pose le ballon rouge sur le tapis. Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8308,7 +8734,23 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Jules se souvient de bleu. Et de le ballon rouge. Et de la poule. Le savon sent bon. Jules sourit. Papa sourit aussi. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>narrateur|La poule picore près de la haie.
+narrateur|Elle fait cot cot, tout petit.
+narrateur|Une plume blonde reste dans l'herbe.
+narrateur|Nino a encore le ballon rouge près du coussin bleu.
+narrateur|L'eau de la carafe tremble près du ballon.
+papa|On dit bonjour à la poule.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans le jardin aussi.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Nino pose le ballon rouge sur le tapis.
+narrateur|Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8336,7 +8778,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Nino a choisi le bleu, le ballon rouge, et la poule. Bravo, Nino. C'est du bon travail. La poule picore encore un grain, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8476,7 +8918,13 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Nino a choisi le bleu, le ballon rouge, et la poule.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La poule picore encore un grain, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8504,7 +8952,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Jules a le seau. Un chat passe. Jules lève la main. Il attend. Puis il parle. On attend. Puis on parle. Papa reste tout près. On peut attendre. Puis on parle. On peut lever la main.</t>
+          <t>Nino prend le seau bleu. Un peu d'eau tremble au fond. Le seau sonne, tout creux. Moi, je raconte l'eau de l'arrosoir. Maman parle. Nino lève la main. Il attend. Je peux verser ? Oui. C'est ton tour. On a attendu. Puis on parle. Nino pose le seau près du tapis. Bravo, Nino. Tu as levé la main. L'eau du seau est un peu bleue, comme le coussin. Le coussin bleu reste sous le genou. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8644,10 +9092,31 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Jules a le seau. Un chat passe. Jules lève la main. Il attend. Puis il parle. On attend. Puis on parle. Papa reste tout près. On peut attendre. Puis on parle. On peut lever la main.</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr"/>
+          <t>narrateur|Nino prend le seau bleu.
+narrateur|Un peu d'eau tremble au fond.
+narrateur|Le seau sonne, tout creux.
+maman|Moi, je raconte l'eau de l'arrosoir.
+narrateur|Maman parle.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Je peux verser ?
+papa|Oui. C'est ton tour.
+papa|On a attendu.
+papa|Puis on parle.
+narrateur|Nino pose le seau près du tapis.
+maman|Bravo, Nino.
+maman|Tu as levé la main.
+narrateur|L'eau du seau est un peu bleue, comme le coussin.
+narrateur|Le coussin bleu reste sous le genou.
+papa|On attend.
+papa|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>seau</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8672,7 +9141,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>Au fond du jardin, trois animaux sont là. Le chat, le chien, ou la poule ? On dit bonjour. Chacun son tour.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8836,7 +9305,10 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|Au fond du jardin, trois animaux sont là.
+papa|Le chat, le chien, ou la poule ?
+maman|On dit bonjour.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
@@ -8868,7 +9340,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Avec le chat. Après le seau bleu. Près de bleu. Jules s'arrête. Un linge sèche à l'air. Jules répète tout bas le geste. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>Le chat s'étire sur la pierre chaude. Ses moustaches bougent. Il fait un petit rrr, tout bas. Nino a encore le seau bleu près du coussin bleu. Le seau fait un son creux. Le chat dresse l'oreille. On dit bonjour à le chat. Nino lève la main. Il attend. Bonjour. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans le jardin aussi. Merci, papa. Merci, maman. Nino pose le seau bleu sur le tapis. Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -9008,7 +9480,24 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Avec le chat. Après le seau bleu. Près de bleu. Jules s'arrête. Un linge sèche à l'air. Jules répète tout bas le geste. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>narrateur|Le chat s'étire sur la pierre chaude.
+narrateur|Ses moustaches bougent.
+narrateur|Il fait un petit rrr, tout bas.
+narrateur|Nino a encore le seau bleu près du coussin bleu.
+narrateur|Le seau fait un son creux.
+narrateur|Le chat dresse l'oreille.
+papa|On dit bonjour à le chat.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans le jardin aussi.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Nino pose le seau bleu sur le tapis.
+narrateur|Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -9036,7 +9525,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Nino a choisi le bleu, le seau bleu, et le chat. Bravo, Nino. C'est du bon travail. Le chat s'endort sur la pierre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9176,7 +9665,13 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Nino a choisi le bleu, le seau bleu, et le chat.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le chat s'endort sur la pierre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9204,7 +9699,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Jules range le seau bleu. le chien reste près de bleu. Le vent est doux. Jules pose le seau bleu à sa place. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>Le chien remue la queue. Son collier fait un toc léger. Il fait wouaf, tout doux. Nino a encore le seau bleu près du coussin bleu. Le chien suit le seau, pas à pas. On dit bonjour à le chien. Nino lève la main. Il attend. Bonjour. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans le jardin aussi. Merci, papa. Merci, maman. Nino pose le seau bleu sur le tapis. Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9344,7 +9839,23 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Jules range le seau bleu. le chien reste près de bleu. Le vent est doux. Jules pose le seau bleu à sa place. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>narrateur|Le chien remue la queue.
+narrateur|Son collier fait un toc léger.
+narrateur|Il fait wouaf, tout doux.
+narrateur|Nino a encore le seau bleu près du coussin bleu.
+narrateur|Le chien suit le seau, pas à pas.
+papa|On dit bonjour à le chien.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans le jardin aussi.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Nino pose le seau bleu sur le tapis.
+narrateur|Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
@@ -9376,7 +9887,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Nino a choisi le bleu, le seau bleu, et le chien. Bravo, Nino. C'est du bon travail. Le chien remue encore la queue, tout lentement. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9516,7 +10027,13 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Nino a choisi le bleu, le seau bleu, et le chien.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le chien remue encore la queue, tout lentement.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9544,7 +10061,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>La poule est là. le seau bleu aussi. bleu reste dans le souvenir. Une feuille tombe. Jules pose sa tête un moment. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>La poule picore près de la haie. Elle fait cot cot, tout petit. Une plume blonde reste dans l'herbe. Nino a encore le seau bleu près du coussin bleu. La poule saute un peu, près du seau. On dit bonjour à la poule. Nino lève la main. Il attend. Bonjour. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans le jardin aussi. Merci, papa. Merci, maman. Nino pose le seau bleu sur le tapis. Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9684,7 +10201,23 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|La poule est là. le seau bleu aussi. bleu reste dans le souvenir. Une feuille tombe. Jules pose sa tête un moment. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>narrateur|La poule picore près de la haie.
+narrateur|Elle fait cot cot, tout petit.
+narrateur|Une plume blonde reste dans l'herbe.
+narrateur|Nino a encore le seau bleu près du coussin bleu.
+narrateur|La poule saute un peu, près du seau.
+papa|On dit bonjour à la poule.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans le jardin aussi.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Nino pose le seau bleu sur le tapis.
+narrateur|Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9712,7 +10245,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Nino a choisi le bleu, le seau bleu, et la poule. Bravo, Nino. C'est du bon travail. La poule picore encore un grain, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9852,7 +10385,13 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Nino a choisi le bleu, le seau bleu, et la poule.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La poule picore encore un grain, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9880,7 +10419,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Jules a le doudou. Un chat passe. Jules lève la main. Il attend. Puis il parle. On attend. Puis on parle. Papa montre le geste, lentement. On peut attendre. Puis on parle. On peut lever la main.</t>
+          <t>Nino prend le doudou. Le doudou est gris, un peu sablé. Une oreille est encore chaude. Le doudou attend, lui aussi. Papa parle tout près. Nino lève la main. Il attend. Le doudou veut parler. Toi d'abord. On attend. Puis on parle. Bravo. Tu as attendu ton tour. Nino serre le doudou, tout doux. Un fil bleu du coussin colle au doudou. Le coussin bleu reste sous le genou. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -10020,7 +10559,24 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Jules a le doudou. Un chat passe. Jules lève la main. Il attend. Puis il parle. On attend. Puis on parle. Papa montre le geste, lentement. On peut attendre. Puis on parle. On peut lever la main.</t>
+          <t>narrateur|Nino prend le doudou.
+narrateur|Le doudou est gris, un peu sablé.
+narrateur|Une oreille est encore chaude.
+papa|Le doudou attend, lui aussi.
+narrateur|Papa parle tout près.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Le doudou veut parler.
+maman|Toi d'abord.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo.
+papa|Tu as attendu ton tour.
+narrateur|Nino serre le doudou, tout doux.
+narrateur|Un fil bleu du coussin colle au doudou.
+narrateur|Le coussin bleu reste sous le genou.
+papa|On attend.
+papa|Puis on parle.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -10048,7 +10604,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>Au fond du jardin, trois animaux sont là. Le chat, le chien, ou la poule ? On dit bonjour. Chacun son tour.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10212,7 +10768,10 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|Au fond du jardin, trois animaux sont là.
+papa|Le chat, le chien, ou la poule ?
+maman|On dit bonjour.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
@@ -10244,7 +10803,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le chat. le doudou est rangé. bleu est fini. On attend son tour. Jules s'assoit près de papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>Le chat s'étire sur la pierre chaude. Ses moustaches bougent. Il fait un petit rrr, tout bas. Nino a encore le doudou près du coussin bleu. Le doudou a un fil bleu. Le chat le touche. On dit bonjour à le chat. Nino lève la main. Il attend. Bonjour. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans le jardin aussi. Merci, papa. Merci, maman. Nino pose le doudou sur le tapis. Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10384,7 +10943,24 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le chat. le doudou est rangé. bleu est fini. On attend son tour. Jules s'assoit près de papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>narrateur|Le chat s'étire sur la pierre chaude.
+narrateur|Ses moustaches bougent.
+narrateur|Il fait un petit rrr, tout bas.
+narrateur|Nino a encore le doudou près du coussin bleu.
+narrateur|Le doudou a un fil bleu.
+narrateur|Le chat le touche.
+papa|On dit bonjour à le chat.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans le jardin aussi.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Nino pose le doudou sur le tapis.
+narrateur|Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10412,7 +10988,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Nino a choisi le bleu, le doudou, et le chat. Bravo, Nino. C'est du bon travail. Le chat s'endort sur la pierre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10552,7 +11128,13 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Nino a choisi le bleu, le doudou, et le chat.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le chat s'endort sur la pierre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10580,7 +11162,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Près de le chien. Jules pose le doudou. bleu est derrière. Un vélo passe au loin. Jules montre le chien à papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>Le chien remue la queue. Son collier fait un toc léger. Il fait wouaf, tout doux. Nino a encore le doudou près du coussin bleu. Le chien s'assoit. Le doudou reste sur les genoux. On dit bonjour à le chien. Nino lève la main. Il attend. Bonjour. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans le jardin aussi. Merci, papa. Merci, maman. Nino pose le doudou sur le tapis. Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10720,7 +11302,24 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Près de le chien. Jules pose le doudou. bleu est derrière. Un vélo passe au loin. Jules montre le chien à papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>narrateur|Le chien remue la queue.
+narrateur|Son collier fait un toc léger.
+narrateur|Il fait wouaf, tout doux.
+narrateur|Nino a encore le doudou près du coussin bleu.
+narrateur|Le chien s'assoit.
+narrateur|Le doudou reste sur les genoux.
+papa|On dit bonjour à le chien.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans le jardin aussi.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Nino pose le doudou sur le tapis.
+narrateur|Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
@@ -10752,7 +11351,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Nino a choisi le bleu, le doudou, et le chien. Bravo, Nino. C'est du bon travail. Le chien remue encore la queue, tout lentement. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10892,7 +11491,13 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Nino a choisi le bleu, le doudou, et le chien.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le chien remue encore la queue, tout lentement.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10920,7 +11525,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Jules montre la poule. Papa a vu bleu. Et le doudou. On se tient la main. Jules enfile ses chaussons. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>La poule picore près de la haie. Elle fait cot cot, tout petit. Une plume blonde reste dans l'herbe. Nino a encore le doudou près du coussin bleu. Un caillou bleu est près de la poule. On dit bonjour à la poule. Nino lève la main. Il attend. Bonjour. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans le jardin aussi. Merci, papa. Merci, maman. Nino pose le doudou sur le tapis. Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11060,7 +11665,23 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Jules montre la poule. Papa a vu bleu. Et le doudou. On se tient la main. Jules enfile ses chaussons. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>narrateur|La poule picore près de la haie.
+narrateur|Elle fait cot cot, tout petit.
+narrateur|Une plume blonde reste dans l'herbe.
+narrateur|Nino a encore le doudou près du coussin bleu.
+narrateur|Un caillou bleu est près de la poule.
+papa|On dit bonjour à la poule.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans le jardin aussi.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Nino pose le doudou sur le tapis.
+narrateur|Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -11088,7 +11709,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Nino a choisi le bleu, le doudou, et la poule. Bravo, Nino. C'est du bon travail. La poule picore encore un grain, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11228,7 +11849,13 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Nino a choisi le bleu, le doudou, et la poule.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La poule picore encore un grain, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11256,7 +11883,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Jules choisit le vert. Les copains parlent fort. Jules lève la main. Il attend. Puis il parle. Chacun son tour. On attend. Puis on parle.</t>
+          <t>Nino choisit le coussin vert. Une petite feuille y est collée. Ça sent l'herbe coupée. Les copains du jardin parlent fort, là-bas. Ici, chacun son tour. Nino lève la main. Il attend. Puis il parle. Le vert, c'est l'herbe. On attend. Puis on parle. Bravo, Nino. Tu as levé la main. Le cerisier bouge un peu. Une ombre passe sur le tapis.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11396,9 +12023,21 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Jules choisit le vert. Les copains parlent fort. Jules lève la main. Il attend. Puis il parle.
-papa|Chacun son tour. On attend.
-narrateur|Puis on parle.</t>
+          <t>narrateur|Nino choisit le coussin vert.
+narrateur|Une petite feuille y est collée.
+narrateur|Ça sent l'herbe coupée.
+papa|Les copains du jardin parlent fort, là-bas.
+papa|Ici, chacun son tour.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+narrateur|Puis il parle.
+enfant-m|Le vert, c'est l'herbe.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo, Nino.
+papa|Tu as levé la main.
+narrateur|Le cerisier bouge un peu.
+narrateur|Une ombre passe sur le tapis.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11426,7 +12065,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>On parle tout de suite, ou on attend ?</t>
+          <t>Chacun son tour, sur le tapis. On attend, puis on parle ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11582,7 +12221,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|On parle tout de suite, ou on attend ?</t>
+          <t>narrateur|Chacun son tour, sur le tapis.
+papa|On attend, puis on parle ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11610,7 +12250,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. On peut attendre. Puis on parle. Jules hoche la tête. On continue, avec papa. On peut attendre. Puis on parle. On peut lever la main.</t>
+          <t>Oui. On attend. Puis on parle. Nino hoche la tête. Chacun son tour. On continue, avec papa. Tu as levé la main. Bravo, Nino.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11754,7 +12394,14 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On peut attendre. Puis on parle. Jules hoche la tête. On continue, avec papa. On peut attendre. Puis on parle. On peut lever la main.</t>
+          <t>papa|Oui.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Nino hoche la tête.
+enfant-m|Chacun son tour.
+maman|On continue, avec papa.
+maman|Tu as levé la main.
+papa|Bravo, Nino.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11782,7 +12429,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>Près du tapis, trois jouets attendent. Le ballon rouge, le seau bleu, ou le doudou ? On joue. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11946,7 +12593,11 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>narrateur|Près du tapis, trois jouets attendent.
+maman|Le ballon rouge, le seau bleu, ou le doudou ?
+papa|On joue.
+papa|On attend.
+papa|Puis on parle.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11974,7 +12625,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Jules a le ballon. Un chien aboie au loin. Jules attend. Puis il parle. On attend. Puis on parle. Papa reste tout près. On peut attendre. Puis on parle. On peut lever la main.</t>
+          <t>Nino prend le ballon rouge. Le ballon est un peu sablé. Il fait poum contre le tapis. J'ai une règle pour le ballon. Papa parle. Nino lève la main. Il attend. C'est ton tour. Le ballon, s'il te plaît. Oui. Merci d'avoir attendu. On attend. Puis on parle. Nino tient le ballon contre son ventre. Bravo. L'herbe tache le ballon, tout vert. Le coussin vert reste sous le genou. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12114,12 +12765,29 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Jules a le ballon. Un chien aboie au loin. Jules attend. Puis il parle. On attend. Puis on parle. Papa reste tout près. On peut attendre. Puis on parle. On peut lever la main.</t>
+          <t>narrateur|Nino prend le ballon rouge.
+narrateur|Le ballon est un peu sablé.
+narrateur|Il fait poum contre le tapis.
+papa|J'ai une règle pour le ballon.
+narrateur|Papa parle.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+papa|C'est ton tour.
+enfant-m|Le ballon, s'il te plaît.
+maman|Oui. Merci d'avoir attendu.
+papa|On attend.
+papa|Puis on parle.
+narrateur|Nino tient le ballon contre son ventre.
+maman|Bravo.
+narrateur|L'herbe tache le ballon, tout vert.
+narrateur|Le coussin vert reste sous le genou.
+papa|On attend.
+papa|Puis on parle.</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>chien_bonjour</t>
+          <t>ballon</t>
         </is>
       </c>
     </row>
@@ -12146,7 +12814,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>Au fond du jardin, trois animaux sont là. Le chat, le chien, ou la poule ? On dit bonjour. Chacun son tour.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12310,7 +12978,10 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|Au fond du jardin, trois animaux sont là.
+papa|Le chat, le chien, ou la poule ?
+maman|On dit bonjour.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
@@ -12342,7 +13013,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Jules a choisi vert. Puis le ballon rouge. Puis le chat. Un chat miaule une fois. Jules écoute papa encore une fois. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>Le chat s'étire sur la pierre chaude. Ses moustaches bougent. Il fait un petit rrr, tout bas. Nino a encore le ballon rouge près du coussin vert. L'herbe tache le ballon. Le chat cligne des yeux. On dit bonjour à le chat. Nino lève la main. Il attend. Bonjour. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans le jardin aussi. Merci, papa. Merci, maman. Nino pose le ballon rouge sur le tapis. Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12482,7 +13153,24 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Jules a choisi vert. Puis le ballon rouge. Puis le chat. Un chat miaule une fois. Jules écoute papa encore une fois. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>narrateur|Le chat s'étire sur la pierre chaude.
+narrateur|Ses moustaches bougent.
+narrateur|Il fait un petit rrr, tout bas.
+narrateur|Nino a encore le ballon rouge près du coussin vert.
+narrateur|L'herbe tache le ballon.
+narrateur|Le chat cligne des yeux.
+papa|On dit bonjour à le chat.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans le jardin aussi.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Nino pose le ballon rouge sur le tapis.
+narrateur|Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12510,7 +13198,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Nino a choisi le vert, le ballon rouge, et le chat. Bravo, Nino. C'est du bon travail. Le chat s'endort sur la pierre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12650,7 +13338,13 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Nino a choisi le vert, le ballon rouge, et le chat.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le chat s'endort sur la pierre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12678,7 +13372,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Jules s'arrête près de le chien. le ballon rouge est rangé. Une tasse cliquette. J'ai appris. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>Le chien remue la queue. Son collier fait un toc léger. Il fait wouaf, tout doux. Nino a encore le ballon rouge près du coussin vert. Le chien court dans l'herbe, puis s'arrête. On dit bonjour à le chien. Nino lève la main. Il attend. Bonjour. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans le jardin aussi. Merci, papa. Merci, maman. Nino pose le ballon rouge sur le tapis. Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12818,9 +13512,23 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Jules s'arrête près de le chien. le ballon rouge est rangé. Une tasse cliquette.
-enfant-m|J'ai appris. On peut attendre.
-narrateur|Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>narrateur|Le chien remue la queue.
+narrateur|Son collier fait un toc léger.
+narrateur|Il fait wouaf, tout doux.
+narrateur|Nino a encore le ballon rouge près du coussin vert.
+narrateur|Le chien court dans l'herbe, puis s'arrête.
+papa|On dit bonjour à le chien.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans le jardin aussi.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Nino pose le ballon rouge sur le tapis.
+narrateur|Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
@@ -12852,7 +13560,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Nino a choisi le vert, le ballon rouge, et le chien. Bravo, Nino. C'est du bon travail. Le chien remue encore la queue, tout lentement. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12992,7 +13700,13 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Nino a choisi le vert, le ballon rouge, et le chien.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le chien remue encore la queue, tout lentement.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -13020,7 +13734,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Jules se souvient de vert. Et de le ballon rouge. Et de la poule. Une pomme brille un peu. Jules range vert dans sa tête, comme un souvenir. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>La poule picore près de la haie. Elle fait cot cot, tout petit. Une plume blonde reste dans l'herbe. Nino a encore le ballon rouge près du coussin vert. La poule traverse l'herbe, près du ballon. On dit bonjour à la poule. Nino lève la main. Il attend. Bonjour. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans le jardin aussi. Merci, papa. Merci, maman. Nino pose le ballon rouge sur le tapis. Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13160,7 +13874,23 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Jules se souvient de vert. Et de le ballon rouge. Et de la poule. Une pomme brille un peu. Jules range vert dans sa tête, comme un souvenir. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>narrateur|La poule picore près de la haie.
+narrateur|Elle fait cot cot, tout petit.
+narrateur|Une plume blonde reste dans l'herbe.
+narrateur|Nino a encore le ballon rouge près du coussin vert.
+narrateur|La poule traverse l'herbe, près du ballon.
+papa|On dit bonjour à la poule.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans le jardin aussi.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Nino pose le ballon rouge sur le tapis.
+narrateur|Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13188,7 +13918,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Nino a choisi le vert, le ballon rouge, et la poule. Bravo, Nino. C'est du bon travail. La poule picore encore un grain, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13328,7 +14058,13 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Nino a choisi le vert, le ballon rouge, et la poule.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La poule picore encore un grain, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13356,7 +14092,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Jules a le seau. Une poule caquette. Jules lève la main. Il attend. Puis il parle. On attend. Puis on parle. Papa montre le geste, lentement. On peut attendre. Puis on parle. On peut lever la main.</t>
+          <t>Nino prend le seau bleu. Un peu d'eau tremble au fond. Le seau sonne, tout creux. Moi, je raconte l'eau de l'arrosoir. Maman parle. Nino lève la main. Il attend. Je peux verser ? Oui. C'est ton tour. On a attendu. Puis on parle. Nino pose le seau près du tapis. Bravo, Nino. Tu as levé la main. Une feuille verte flotte dans le seau. Le coussin vert reste sous le genou. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13496,10 +14232,31 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Jules a le seau. Une poule caquette. Jules lève la main. Il attend. Puis il parle. On attend. Puis on parle. Papa montre le geste, lentement. On peut attendre. Puis on parle. On peut lever la main.</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr"/>
+          <t>narrateur|Nino prend le seau bleu.
+narrateur|Un peu d'eau tremble au fond.
+narrateur|Le seau sonne, tout creux.
+maman|Moi, je raconte l'eau de l'arrosoir.
+narrateur|Maman parle.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Je peux verser ?
+papa|Oui. C'est ton tour.
+papa|On a attendu.
+papa|Puis on parle.
+narrateur|Nino pose le seau près du tapis.
+maman|Bravo, Nino.
+maman|Tu as levé la main.
+narrateur|Une feuille verte flotte dans le seau.
+narrateur|Le coussin vert reste sous le genou.
+papa|On attend.
+papa|Puis on parle.</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>seau</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13524,7 +14281,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>Au fond du jardin, trois animaux sont là. Le chat, le chien, ou la poule ? On dit bonjour. Chacun son tour.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13688,7 +14445,10 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|Au fond du jardin, trois animaux sont là.
+papa|Le chat, le chien, ou la poule ?
+maman|On dit bonjour.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
@@ -13720,7 +14480,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Avec le chat. Après le seau bleu. Près de vert. Jules s'arrête. Les chaussures font toc toc. Jules chuchote : c'est fini. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>Le chat s'étire sur la pierre chaude. Ses moustaches bougent. Il fait un petit rrr, tout bas. Nino a encore le seau bleu près du coussin vert. Une feuille verte flotte. Le chat la suit des yeux. On dit bonjour à le chat. Nino lève la main. Il attend. Bonjour. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans le jardin aussi. Merci, papa. Merci, maman. Nino pose le seau bleu sur le tapis. Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13860,7 +14620,24 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Avec le chat. Après le seau bleu. Près de vert. Jules s'arrête. Les chaussures font toc toc. Jules chuchote : c'est fini. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>narrateur|Le chat s'étire sur la pierre chaude.
+narrateur|Ses moustaches bougent.
+narrateur|Il fait un petit rrr, tout bas.
+narrateur|Nino a encore le seau bleu près du coussin vert.
+narrateur|Une feuille verte flotte.
+narrateur|Le chat la suit des yeux.
+papa|On dit bonjour à le chat.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans le jardin aussi.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Nino pose le seau bleu sur le tapis.
+narrateur|Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13888,7 +14665,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Nino a choisi le vert, le seau bleu, et le chat. Bravo, Nino. C'est du bon travail. Le chat s'endort sur la pierre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -14028,7 +14805,13 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Nino a choisi le vert, le seau bleu, et le chat.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le chat s'endort sur la pierre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14056,7 +14839,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Jules range le seau bleu. le chien reste près de vert. La couverture est douce. Jules dit merci à papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>Le chien remue la queue. Son collier fait un toc léger. Il fait wouaf, tout doux. Nino a encore le seau bleu près du coussin vert. Le chien renifle le seau, puis s'arrête. On dit bonjour à le chien. Nino lève la main. Il attend. Bonjour. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans le jardin aussi. Merci, papa. Merci, maman. Nino pose le seau bleu sur le tapis. Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14196,7 +14979,23 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Jules range le seau bleu. le chien reste près de vert. La couverture est douce. Jules dit merci à papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>narrateur|Le chien remue la queue.
+narrateur|Son collier fait un toc léger.
+narrateur|Il fait wouaf, tout doux.
+narrateur|Nino a encore le seau bleu près du coussin vert.
+narrateur|Le chien renifle le seau, puis s'arrête.
+papa|On dit bonjour à le chien.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans le jardin aussi.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Nino pose le seau bleu sur le tapis.
+narrateur|Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
@@ -14228,7 +15027,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Nino a choisi le vert, le seau bleu, et le chien. Bravo, Nino. C'est du bon travail. Le chien remue encore la queue, tout lentement. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14368,7 +15167,13 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Nino a choisi le vert, le seau bleu, et le chien.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le chien remue encore la queue, tout lentement.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14396,7 +15201,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>La poule est là. le seau bleu aussi. vert reste dans le souvenir. On dit merci. Jules caresse le doudou. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>La poule picore près de la haie. Elle fait cot cot, tout petit. Une plume blonde reste dans l'herbe. Nino a encore le seau bleu près du coussin vert. La poule cherche un ver. Nino attend. On dit bonjour à la poule. Nino lève la main. Il attend. Bonjour. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans le jardin aussi. Merci, papa. Merci, maman. Nino pose le seau bleu sur le tapis. Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14536,7 +15341,24 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|La poule est là. le seau bleu aussi. vert reste dans le souvenir. On dit merci. Jules caresse le doudou. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>narrateur|La poule picore près de la haie.
+narrateur|Elle fait cot cot, tout petit.
+narrateur|Une plume blonde reste dans l'herbe.
+narrateur|Nino a encore le seau bleu près du coussin vert.
+narrateur|La poule cherche un ver.
+narrateur|Nino attend.
+papa|On dit bonjour à la poule.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans le jardin aussi.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Nino pose le seau bleu sur le tapis.
+narrateur|Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14564,7 +15386,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Nino a choisi le vert, le seau bleu, et la poule. Bravo, Nino. C'est du bon travail. La poule picore encore un grain, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14704,7 +15526,13 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Nino a choisi le vert, le seau bleu, et la poule.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La poule picore encore un grain, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14732,7 +15560,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Jules a le doudou. Une poule caquette. Jules lève la main. Il attend. Puis il parle. On attend. Puis on parle. Je suis là. On peut attendre. Puis on parle. On peut lever la main.</t>
+          <t>Nino prend le doudou. Le doudou est gris, un peu sablé. Une oreille est encore chaude. Le doudou attend, lui aussi. Papa parle tout près. Nino lève la main. Il attend. Le doudou veut parler. Toi d'abord. On attend. Puis on parle. Bravo. Tu as attendu ton tour. Nino serre le doudou, tout doux. Le doudou a une tache d'herbe. Le coussin vert reste sous le genou. On attend. Puis on parle.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14872,9 +15700,24 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Jules a le doudou. Une poule caquette. Jules lève la main. Il attend. Puis il parle. On attend. Puis on parle.
-papa|Je suis là. On peut attendre.
-narrateur|Puis on parle. On peut lever la main.</t>
+          <t>narrateur|Nino prend le doudou.
+narrateur|Le doudou est gris, un peu sablé.
+narrateur|Une oreille est encore chaude.
+papa|Le doudou attend, lui aussi.
+narrateur|Papa parle tout près.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Le doudou veut parler.
+maman|Toi d'abord.
+maman|On attend.
+maman|Puis on parle.
+papa|Bravo.
+papa|Tu as attendu ton tour.
+narrateur|Nino serre le doudou, tout doux.
+narrateur|Le doudou a une tache d'herbe.
+narrateur|Le coussin vert reste sous le genou.
+papa|On attend.
+papa|Puis on parle.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14902,7 +15745,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le chat, le chien, ou la poule.</t>
+          <t>Au fond du jardin, trois animaux sont là. Le chat, le chien, ou la poule ? On dit bonjour. Chacun son tour.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15066,7 +15909,10 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+          <t>narrateur|Au fond du jardin, trois animaux sont là.
+papa|Le chat, le chien, ou la poule ?
+maman|On dit bonjour.
+maman|Chacun son tour.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
@@ -15098,7 +15944,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le chat. le doudou est rangé. vert est fini. On écoute jusqu'au bout. Maman n'est pas loin. Jules les rejoint. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>Le chat s'étire sur la pierre chaude. Ses moustaches bougent. Il fait un petit rrr, tout bas. Nino a encore le doudou près du coussin vert. Le doudou a une tache d'herbe. Le chat ronronne. On dit bonjour à le chat. Nino lève la main. Il attend. Bonjour. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans le jardin aussi. Merci, papa. Merci, maman. Nino pose le doudou sur le tapis. Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15238,7 +16084,24 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le chat. le doudou est rangé. vert est fini. On écoute jusqu'au bout. Maman n'est pas loin. Jules les rejoint. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>narrateur|Le chat s'étire sur la pierre chaude.
+narrateur|Ses moustaches bougent.
+narrateur|Il fait un petit rrr, tout bas.
+narrateur|Nino a encore le doudou près du coussin vert.
+narrateur|Le doudou a une tache d'herbe.
+narrateur|Le chat ronronne.
+papa|On dit bonjour à le chat.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans le jardin aussi.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Nino pose le doudou sur le tapis.
+narrateur|Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15266,7 +16129,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Nino a choisi le vert, le doudou, et le chat. Bravo, Nino. C'est du bon travail. Le chat s'endort sur la pierre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15406,7 +16269,13 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Nino a choisi le vert, le doudou, et le chat.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le chat s'endort sur la pierre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15434,7 +16303,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Près de le chien. Jules pose le doudou. vert est derrière. Un crochet tient bien le manteau. Jules range la tasse. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>Le chien remue la queue. Son collier fait un toc léger. Il fait wouaf, tout doux. Nino a encore le doudou près du coussin vert. Le chien pose la tête près du doudou. On dit bonjour à le chien. Nino lève la main. Il attend. Bonjour. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans le jardin aussi. Merci, papa. Merci, maman. Nino pose le doudou sur le tapis. Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15574,7 +16443,23 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Près de le chien. Jules pose le doudou. vert est derrière. Un crochet tient bien le manteau. Jules range la tasse. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>narrateur|Le chien remue la queue.
+narrateur|Son collier fait un toc léger.
+narrateur|Il fait wouaf, tout doux.
+narrateur|Nino a encore le doudou près du coussin vert.
+narrateur|Le chien pose la tête près du doudou.
+papa|On dit bonjour à le chien.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans le jardin aussi.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Nino pose le doudou sur le tapis.
+narrateur|Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
@@ -15606,7 +16491,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Nino a choisi le vert, le doudou, et le chien. Bravo, Nino. C'est du bon travail. Le chien remue encore la queue, tout lentement. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15746,7 +16631,13 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Nino a choisi le vert, le doudou, et le chien.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|Le chien remue encore la queue, tout lentement.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15774,7 +16665,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Jules montre la poule. Papa a vu vert. Et le doudou. On entend un oiseau. Jules prend la main de papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>La poule picore près de la haie. Elle fait cot cot, tout petit. Une plume blonde reste dans l'herbe. Nino a encore le doudou près du coussin vert. La poule s'arrête. Le doudou reste calme. On dit bonjour à la poule. Nino lève la main. Il attend. Bonjour. Bravo. Tu as attendu. Puis tu as parlé. On peut lever la main, dans le jardin aussi. Merci, papa. Merci, maman. Nino pose le doudou sur le tapis. Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15914,7 +16805,24 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Jules montre la poule. Papa a vu vert. Et le doudou. On entend un oiseau. Jules prend la main de papa. On peut attendre. Puis on parle. On peut lever la main. On lève la main. On peut attendre. Puis on parle. Jules dit merci à papa.</t>
+          <t>narrateur|La poule picore près de la haie.
+narrateur|Elle fait cot cot, tout petit.
+narrateur|Une plume blonde reste dans l'herbe.
+narrateur|Nino a encore le doudou près du coussin vert.
+narrateur|La poule s'arrête.
+narrateur|Le doudou reste calme.
+papa|On dit bonjour à la poule.
+narrateur|Nino lève la main.
+narrateur|Il attend.
+enfant-m|Bonjour.
+maman|Bravo.
+maman|Tu as attendu.
+maman|Puis tu as parlé.
+papa|On peut lever la main, dans le jardin aussi.
+enfant-m|Merci, papa.
+enfant-m|Merci, maman.
+narrateur|Nino pose le doudou sur le tapis.
+narrateur|Le cerisier fait une ombre ronde.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15942,7 +16850,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as attendu. Puis tu as parlé. Nino a choisi le vert, le doudou, et la poule. Bravo, Nino. C'est du bon travail. La poule picore encore un grain, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16082,7 +16990,13 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as attendu.
+maman|Puis tu as parlé.
+narrateur|Nino a choisi le vert, le doudou, et la poule.
+papa|Bravo, Nino.
+papa|C'est du bon travail.
+narrateur|La poule picore encore un grain, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16104,7 +17018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16142,6 +17056,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-003.xlsx
+++ b/stories/arbres/TREE-COL-003.xlsx
@@ -1197,17 +1197,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le tapis rouge, plié en boudin, roule hors des bras de papa. Il s'ouvre, chaud, avec une odeur de foin. Un grain de cerise glisse hors d'un pli. Le grain s'arrête, collé au bec de l'arrosoir. L'arrosoir vert est lourd, un peu bosselé. Le campement du cerisier sent la terre sèche. Maman pose la carafe, et un coussin rayé. Raphaël, l'eau, pour le pied de l'arbre. Le tapis est prêt, les genoux aussi. En ce moment, Raphaël saisit l'anse, trop vite. Je veux arroser, maintenant ! Mila arrive, les joues chaudes, les mains ouvertes. Je veux le tapis, pour raconter ! Les deux voix partent ensemble, trop fort. Papa tourne la carafe, il n'entend qu'un mélange. J'ai entendu un mélange. On n'a rien compris. Le sourire de Raphaël disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. La terre a soif ! Mila parle par-dessus, les mots se cognent. Personne ne se tourne. Le grain de cerise reste collé au bec, minuscule.</t>
+          <t>Le tapis rouge, plié en boudin, roule hors des bras de papa. Il s'ouvre, chaud, avec une odeur de foin. Un grain de cerise glisse hors d'un pli. Le grain s'arrête, collé au bec de l'arrosoir. L'arrosoir vert, lourd et bosselé, attend au campement du cerisier. Maman pose la carafe, et un coussin rayé. Raphaël, l'eau, pour le pied de l'arbre. Le tapis est prêt, les genoux aussi. En ce moment, Raphaël saisit l'anse, trop vite. Je veux arroser, maintenant ! Mila arrive, les joues chaudes, les mains ouvertes. Je veux le tapis, pour raconter ! Les deux voix partent ensemble, trop fort. Papa tourne la carafe, il n'entend qu'un mélange. J'ai entendu un mélange. On n'a rien compris. Le sourire de Raphaël disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. La terre a soif ! Mila parle par-dessus, les mots se cognent. Personne ne se tourne. Le grain de cerise reste collé au bec, minuscule.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le tapis rouge, plié en boudin, roule hors des bras de papa. Il s'ouvre, chaud, avec une odeur de foin. Un &lt;emphasis level="moderate"&gt;grain de cerise&lt;/emphasis&gt; glisse hors d'un pli. Le grain s'arrête, collé au bec de l'arrosoir. L'arrosoir vert est lourd, un peu bosselé. Le campement du cerisier sent la terre sèche. Maman pose la carafe, et un coussin rayé. Raphaël, l'eau, pour le pied de l'arbre. Le tapis est prêt, les genoux aussi. En ce moment, Raphaël saisit l'anse, trop vite. Je veux arroser, maintenant ! Mila arrive, les joues chaudes, les mains ouvertes. Je veux le tapis, pour raconter ! Les deux voix partent ensemble, trop fort. Papa tourne la carafe, il n'entend qu'un mélange. J'ai entendu un mélange. On n'a rien compris. Le sourire de Raphaël disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. La terre a soif ! Mila parle par-dessus, les mots se cognent. Personne ne se tourne. Le grain de cerise reste collé au bec, minuscule.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le tapis rouge, plié en boudin, roule hors des bras de papa. Il s'ouvre, chaud, avec une odeur de foin. Un &lt;emphasis level="moderate"&gt;grain de cerise&lt;/emphasis&gt; glisse hors d'un pli. Le grain s'arrête, collé au bec de l'arrosoir. L'arrosoir vert, lourd et bosselé, attend au campement du cerisier. Maman pose la carafe, et un coussin rayé. Raphaël, l'eau, pour le pied de l'arbre. Le tapis est prêt, les genoux aussi. En ce moment, Raphaël saisit l'anse, trop vite. Je veux arroser, maintenant ! Mila arrive, les joues chaudes, les mains ouvertes. Je veux le tapis, pour raconter ! Les deux voix partent ensemble, trop fort. Papa tourne la carafe, il n'entend qu'un mélange. J'ai entendu un mélange. On n'a rien compris. Le sourire de Raphaël disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. La terre a soif ! Mila parle par-dessus, les mots se cognent. Personne ne se tourne. Le grain de cerise reste collé au bec, minuscule.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Le tapis rouge, plié en boudin, roule hors des bras de papa. Il s'ouvre, chaud, avec une odeur de foin. Un &lt;emphasis&gt;grain de cerise&lt;/emphasis&gt; glisse hors d'un pli. Le grain s'arrête, collé au bec de l'arrosoir. L'arrosoir vert est lourd, un peu bosselé. Le campement du cerisier sent la terre sèche. Maman pose la carafe, et un coussin rayé. Raphaël, l'eau, pour le pied de l'arbre. Le tapis est prêt, les genoux aussi. En ce moment, Raphaël saisit l'anse, trop vite. Je veux arroser, maintenant ! Mila arrive, les joues chaudes, les mains ouvertes. Je veux le tapis, pour raconter ! Les deux voix partent ensemble, trop fort. Papa tourne la carafe, il n'entend qu'un mélange. J'ai entendu un mélange. On n'a rien compris. Le sourire de Raphaël disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. La terre a soif ! Mila parle par-dessus, les mots se cognent. Personne ne se tourne. Le grain de cerise reste collé au bec, minuscule. [pause]</t>
+          <t>Le tapis rouge, plié en boudin, roule hors des bras de papa. Il s'ouvre, chaud, avec une odeur de foin. Un &lt;emphasis&gt;grain de cerise&lt;/emphasis&gt; glisse hors d'un pli. Le grain s'arrête, collé au bec de l'arrosoir. L'arrosoir vert, lourd et bosselé, attend au campement du cerisier. Maman pose la carafe, et un coussin rayé. Raphaël, l'eau, pour le pied de l'arbre. Le tapis est prêt, les genoux aussi. En ce moment, Raphaël saisit l'anse, trop vite. Je veux arroser, maintenant ! Mila arrive, les joues chaudes, les mains ouvertes. Je veux le tapis, pour raconter ! Les deux voix partent ensemble, trop fort. Papa tourne la carafe, il n'entend qu'un mélange. J'ai entendu un mélange. On n'a rien compris. Le sourire de Raphaël disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. La terre a soif ! Mila parle par-dessus, les mots se cognent. Personne ne se tourne. Le grain de cerise reste collé au bec, minuscule. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1345,8 +1345,7 @@
 narrateur|Il s'ouvre, chaud, avec une odeur de foin.
 narrateur|Un grain de cerise glisse hors d'un pli.
 narrateur|Le grain s'arrête, collé au bec de l'arrosoir.
-narrateur|L'arrosoir vert est lourd, un peu bosselé.
-narrateur|Le campement du cerisier sent la terre sèche.
+narrateur|L'arrosoir vert, lourd et bosselé, attend au campement du cerisier.
 narrateur|Maman pose la carafe, et un coussin rayé.
 papa|Raphaël, l'eau, pour le pied de l'arbre.
 maman|Le tapis est prêt, les genoux aussi.
@@ -17548,7 +17547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17605,6 +17604,13 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
